--- a/Config/Config.xlsx
+++ b/Config/Config.xlsx
@@ -5,11 +5,11 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\tml-integration_branch\Config\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\TML_Process_GIT\TML_Project\Config\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="20490" windowHeight="7530"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="12210"/>
   </bookViews>
   <sheets>
     <sheet name="Config" sheetId="1" r:id="rId1"/>
@@ -94,9 +94,6 @@
     <t>benly.polly@quadance.com</t>
   </si>
   <si>
-    <t>C:/tml-integration_branch/Config/Config - Copy 2.xlsx</t>
-  </si>
-  <si>
     <t>Sheet2</t>
   </si>
   <si>
@@ -104,6 +101,9 @@
   </si>
   <si>
     <t>ClientConfigSheetName2</t>
+  </si>
+  <si>
+    <t>D:/TML_Process_GIT/TML_Project/Config/Client_Config.xlsx</t>
   </si>
 </sst>
 </file>
@@ -523,7 +523,7 @@
         <v>2</v>
       </c>
       <c r="B3" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
     </row>
     <row r="4" spans="1:2">
@@ -560,10 +560,10 @@
     </row>
     <row r="8" spans="1:2">
       <c r="A8" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B8" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="9" spans="1:2">
@@ -571,7 +571,7 @@
         <v>8</v>
       </c>
       <c r="B9" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
     </row>
     <row r="10" spans="1:2">
@@ -615,6 +615,17 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <TaxCatchAll xmlns="399697c3-5931-482a-bf60-528e1410a718" xsi:nil="true"/>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="69774094-9380-4fae-b934-13dda1a7dd00">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+  </documentManagement>
+</p:properties>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <?mso-contentType ?>
 <FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
   <Display>DocumentLibraryForm</Display>
@@ -623,7 +634,7 @@
 </FormTemplates>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x01010044376E494BD8C84F84CDAE7F49671CB7" ma:contentTypeVersion="18" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="976d064ff5353b1784c9cc50294987ed">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="69774094-9380-4fae-b934-13dda1a7dd00" xmlns:ns3="399697c3-5931-482a-bf60-528e1410a718" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="6d25ac32989da96868f130ee3b29a1a8" ns2:_="" ns3:_="">
     <xsd:import namespace="69774094-9380-4fae-b934-13dda1a7dd00"/>
@@ -878,18 +889,18 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <TaxCatchAll xmlns="399697c3-5931-482a-bf60-528e1410a718" xsi:nil="true"/>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="69774094-9380-4fae-b934-13dda1a7dd00">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-  </documentManagement>
-</p:properties>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E2F655CD-E750-4B4F-AAB6-574220BB7DEF}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="399697c3-5931-482a-bf60-528e1410a718"/>
+    <ds:schemaRef ds:uri="69774094-9380-4fae-b934-13dda1a7dd00"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{4B24F227-3507-4068-BCE6-AC132C9C6BAF}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
@@ -897,7 +908,7 @@
 </ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{14112939-A704-4318-9B1F-3D369493ECFB}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -914,15 +925,4 @@
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E2F655CD-E750-4B4F-AAB6-574220BB7DEF}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="399697c3-5931-482a-bf60-528e1410a718"/>
-    <ds:schemaRef ds:uri="69774094-9380-4fae-b934-13dda1a7dd00"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
 </file>
--- a/Config/Config.xlsx
+++ b/Config/Config.xlsx
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="23" uniqueCount="23">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="25" uniqueCount="25">
   <si>
     <t>Name</t>
   </si>
@@ -104,6 +104,12 @@
   </si>
   <si>
     <t>D:/TML_Process_GIT/TML_Project/Config/Client_Config.xlsx</t>
+  </si>
+  <si>
+    <t>ClaimsFolderPath</t>
+  </si>
+  <si>
+    <t>D:/TML_Claims/</t>
   </si>
 </sst>
 </file>
@@ -598,6 +604,14 @@
         <v>16</v>
       </c>
     </row>
+    <row r="13" spans="1:2">
+      <c r="A13" t="s">
+        <v>23</v>
+      </c>
+      <c r="B13" t="s">
+        <v>24</v>
+      </c>
+    </row>
     <row r="16" spans="1:2">
       <c r="B16" s="2"/>
     </row>
@@ -626,15 +640,6 @@
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x01010044376E494BD8C84F84CDAE7F49671CB7" ma:contentTypeVersion="18" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="976d064ff5353b1784c9cc50294987ed">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="69774094-9380-4fae-b934-13dda1a7dd00" xmlns:ns3="399697c3-5931-482a-bf60-528e1410a718" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="6d25ac32989da96868f130ee3b29a1a8" ns2:_="" ns3:_="">
     <xsd:import namespace="69774094-9380-4fae-b934-13dda1a7dd00"/>
@@ -889,6 +894,15 @@
 </ct:contentTypeSchema>
 </file>
 
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E2F655CD-E750-4B4F-AAB6-574220BB7DEF}">
   <ds:schemaRefs>
@@ -901,14 +915,6 @@
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{4B24F227-3507-4068-BCE6-AC132C9C6BAF}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{14112939-A704-4318-9B1F-3D369493ECFB}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -925,4 +931,12 @@
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{4B24F227-3507-4068-BCE6-AC132C9C6BAF}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
--- a/Config/Config.xlsx
+++ b/Config/Config.xlsx
@@ -109,7 +109,7 @@
     <t>ClaimsFolderPath</t>
   </si>
   <si>
-    <t>D:/TML_Claims/</t>
+    <t>D:/TML_Claims</t>
   </si>
 </sst>
 </file>

--- a/Config/Config.xlsx
+++ b/Config/Config.xlsx
@@ -91,9 +91,6 @@
     <t>vishnu.s@quadance.com;benly.polly@quadance.com</t>
   </si>
   <si>
-    <t>benly.polly@quadance.com</t>
-  </si>
-  <si>
     <t>Sheet2</t>
   </si>
   <si>
@@ -110,6 +107,9 @@
   </si>
   <si>
     <t>D:/TML_Claims</t>
+  </si>
+  <si>
+    <t>tmlclaims.ho@pmmil.com</t>
   </si>
 </sst>
 </file>
@@ -529,7 +529,7 @@
         <v>2</v>
       </c>
       <c r="B3" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="4" spans="1:2">
@@ -545,7 +545,7 @@
         <v>4</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>18</v>
+        <v>24</v>
       </c>
     </row>
     <row r="6" spans="1:2">
@@ -566,10 +566,10 @@
     </row>
     <row r="8" spans="1:2">
       <c r="A8" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="B8" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
     </row>
     <row r="9" spans="1:2">
@@ -577,7 +577,7 @@
         <v>8</v>
       </c>
       <c r="B9" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="10" spans="1:2">
@@ -606,10 +606,10 @@
     </row>
     <row r="13" spans="1:2">
       <c r="A13" t="s">
+        <v>22</v>
+      </c>
+      <c r="B13" t="s">
         <v>23</v>
-      </c>
-      <c r="B13" t="s">
-        <v>24</v>
       </c>
     </row>
     <row r="16" spans="1:2">
@@ -622,9 +622,10 @@
   <hyperlinks>
     <hyperlink ref="B4" r:id="rId1"/>
     <hyperlink ref="B2" r:id="rId2"/>
+    <hyperlink ref="B5" r:id="rId3"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" r:id="rId3"/>
+  <pageSetup orientation="portrait" r:id="rId4"/>
 </worksheet>
 </file>
 
@@ -640,6 +641,15 @@
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x01010044376E494BD8C84F84CDAE7F49671CB7" ma:contentTypeVersion="18" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="976d064ff5353b1784c9cc50294987ed">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="69774094-9380-4fae-b934-13dda1a7dd00" xmlns:ns3="399697c3-5931-482a-bf60-528e1410a718" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="6d25ac32989da96868f130ee3b29a1a8" ns2:_="" ns3:_="">
     <xsd:import namespace="69774094-9380-4fae-b934-13dda1a7dd00"/>
@@ -894,15 +904,6 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E2F655CD-E750-4B4F-AAB6-574220BB7DEF}">
   <ds:schemaRefs>
@@ -915,6 +916,14 @@
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{4B24F227-3507-4068-BCE6-AC132C9C6BAF}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{14112939-A704-4318-9B1F-3D369493ECFB}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -931,12 +940,4 @@
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{4B24F227-3507-4068-BCE6-AC132C9C6BAF}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
 </file>
--- a/Config/Config.xlsx
+++ b/Config/Config.xlsx
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="25" uniqueCount="25">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="26" uniqueCount="26">
   <si>
     <t>Name</t>
   </si>
@@ -58,9 +58,6 @@
     <t>https://portal.cvnextgenapps.tatamotors.com/</t>
   </si>
   <si>
-    <t>Sheet1</t>
-  </si>
-  <si>
     <t>ClientConfigPath</t>
   </si>
   <si>
@@ -91,9 +88,6 @@
     <t>vishnu.s@quadance.com;benly.polly@quadance.com</t>
   </si>
   <si>
-    <t>Sheet2</t>
-  </si>
-  <si>
     <t>chrome</t>
   </si>
   <si>
@@ -109,7 +103,16 @@
     <t>D:/TML_Claims</t>
   </si>
   <si>
-    <t>tmlclaims.ho@pmmil.com</t>
+    <t>CleanUpDayCount</t>
+  </si>
+  <si>
+    <t>Other_Credentials</t>
+  </si>
+  <si>
+    <t>Login_Credentials</t>
+  </si>
+  <si>
+    <t>vishnu.s@quadance.com</t>
   </si>
 </sst>
 </file>
@@ -518,7 +521,7 @@
     </row>
     <row r="2" spans="1:2">
       <c r="A2" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B2" s="2" t="s">
         <v>6</v>
@@ -529,7 +532,7 @@
         <v>2</v>
       </c>
       <c r="B3" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
     </row>
     <row r="4" spans="1:2">
@@ -537,7 +540,7 @@
         <v>3</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
     </row>
     <row r="5" spans="1:2">
@@ -545,7 +548,7 @@
         <v>4</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
     </row>
     <row r="6" spans="1:2">
@@ -558,58 +561,66 @@
     </row>
     <row r="7" spans="1:2">
       <c r="A7" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B7" t="s">
-        <v>7</v>
+        <v>24</v>
       </c>
     </row>
     <row r="8" spans="1:2">
       <c r="A8" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="B8" t="s">
-        <v>18</v>
+        <v>23</v>
       </c>
     </row>
     <row r="9" spans="1:2">
       <c r="A9" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B9" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
     </row>
     <row r="10" spans="1:2">
       <c r="A10" t="s">
+        <v>10</v>
+      </c>
+      <c r="B10" t="s">
         <v>11</v>
-      </c>
-      <c r="B10" t="s">
-        <v>12</v>
       </c>
     </row>
     <row r="11" spans="1:2">
       <c r="A11" t="s">
+        <v>12</v>
+      </c>
+      <c r="B11" t="s">
         <v>13</v>
-      </c>
-      <c r="B11" t="s">
-        <v>14</v>
       </c>
     </row>
     <row r="12" spans="1:2">
       <c r="A12" t="s">
+        <v>14</v>
+      </c>
+      <c r="B12" t="s">
         <v>15</v>
-      </c>
-      <c r="B12" t="s">
-        <v>16</v>
       </c>
     </row>
     <row r="13" spans="1:2">
       <c r="A13" t="s">
+        <v>20</v>
+      </c>
+      <c r="B13" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="14" spans="1:2">
+      <c r="A14" t="s">
         <v>22</v>
       </c>
-      <c r="B13" t="s">
-        <v>23</v>
+      <c r="B14">
+        <v>7</v>
       </c>
     </row>
     <row r="16" spans="1:2">

--- a/Config/Config.xlsx
+++ b/Config/Config.xlsx
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="26" uniqueCount="26">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="22" uniqueCount="22">
   <si>
     <t>Name</t>
   </si>
@@ -46,12 +46,6 @@
     <t>Browser</t>
   </si>
   <si>
-    <t>RecipientTo</t>
-  </si>
-  <si>
-    <t>RecipientCc</t>
-  </si>
-  <si>
     <t>RetryCount</t>
   </si>
   <si>
@@ -85,9 +79,6 @@
     <t>TML</t>
   </si>
   <si>
-    <t>vishnu.s@quadance.com;benly.polly@quadance.com</t>
-  </si>
-  <si>
     <t>chrome</t>
   </si>
   <si>
@@ -110,9 +101,6 @@
   </si>
   <si>
     <t>Login_Credentials</t>
-  </si>
-  <si>
-    <t>vishnu.s@quadance.com</t>
   </si>
 </sst>
 </file>
@@ -504,7 +492,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:B17"/>
+  <dimension ref="A1:B15"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <cols>
     <col min="1" max="1" width="40.875" customWidth="1"/>
@@ -521,10 +509,10 @@
     </row>
     <row r="2" spans="1:2">
       <c r="A2" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>6</v>
+        <v>4</v>
       </c>
     </row>
     <row r="3" spans="1:2">
@@ -532,111 +520,93 @@
         <v>2</v>
       </c>
       <c r="B3" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
     </row>
     <row r="4" spans="1:2">
       <c r="A4" t="s">
         <v>3</v>
       </c>
-      <c r="B4" s="2" t="s">
-        <v>16</v>
+      <c r="B4">
+        <v>3</v>
       </c>
     </row>
     <row r="5" spans="1:2">
       <c r="A5" t="s">
-        <v>4</v>
-      </c>
-      <c r="B5" s="2" t="s">
-        <v>25</v>
+        <v>6</v>
+      </c>
+      <c r="B5" t="s">
+        <v>21</v>
       </c>
     </row>
     <row r="6" spans="1:2">
       <c r="A6" t="s">
-        <v>5</v>
-      </c>
-      <c r="B6">
-        <v>3</v>
+        <v>15</v>
+      </c>
+      <c r="B6" t="s">
+        <v>20</v>
       </c>
     </row>
     <row r="7" spans="1:2">
       <c r="A7" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="B7" t="s">
-        <v>24</v>
+        <v>16</v>
       </c>
     </row>
     <row r="8" spans="1:2">
       <c r="A8" t="s">
-        <v>18</v>
+        <v>8</v>
       </c>
       <c r="B8" t="s">
-        <v>23</v>
+        <v>9</v>
       </c>
     </row>
     <row r="9" spans="1:2">
       <c r="A9" t="s">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="B9" t="s">
-        <v>19</v>
+        <v>11</v>
       </c>
     </row>
     <row r="10" spans="1:2">
       <c r="A10" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="B10" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
     </row>
     <row r="11" spans="1:2">
       <c r="A11" t="s">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="B11" t="s">
-        <v>13</v>
+        <v>18</v>
       </c>
     </row>
     <row r="12" spans="1:2">
       <c r="A12" t="s">
-        <v>14</v>
-      </c>
-      <c r="B12" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="13" spans="1:2">
-      <c r="A13" t="s">
-        <v>20</v>
-      </c>
-      <c r="B13" t="s">
-        <v>21</v>
+        <v>19</v>
+      </c>
+      <c r="B12">
+        <v>7</v>
       </c>
     </row>
     <row r="14" spans="1:2">
-      <c r="A14" t="s">
-        <v>22</v>
-      </c>
-      <c r="B14">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="16" spans="1:2">
-      <c r="B16" s="2"/>
-    </row>
-    <row r="17" spans="2:2">
-      <c r="B17" s="2"/>
+      <c r="B14" s="2"/>
+    </row>
+    <row r="15" spans="1:2">
+      <c r="B15" s="2"/>
     </row>
   </sheetData>
   <hyperlinks>
-    <hyperlink ref="B4" r:id="rId1"/>
-    <hyperlink ref="B2" r:id="rId2"/>
-    <hyperlink ref="B5" r:id="rId3"/>
+    <hyperlink ref="B2" r:id="rId1"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" r:id="rId4"/>
+  <pageSetup orientation="portrait" r:id="rId2"/>
 </worksheet>
 </file>
 
@@ -652,15 +622,6 @@
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x01010044376E494BD8C84F84CDAE7F49671CB7" ma:contentTypeVersion="18" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="976d064ff5353b1784c9cc50294987ed">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="69774094-9380-4fae-b934-13dda1a7dd00" xmlns:ns3="399697c3-5931-482a-bf60-528e1410a718" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="6d25ac32989da96868f130ee3b29a1a8" ns2:_="" ns3:_="">
     <xsd:import namespace="69774094-9380-4fae-b934-13dda1a7dd00"/>
@@ -915,6 +876,15 @@
 </ct:contentTypeSchema>
 </file>
 
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E2F655CD-E750-4B4F-AAB6-574220BB7DEF}">
   <ds:schemaRefs>
@@ -927,14 +897,6 @@
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{4B24F227-3507-4068-BCE6-AC132C9C6BAF}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{14112939-A704-4318-9B1F-3D369493ECFB}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -951,4 +913,12 @@
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{4B24F227-3507-4068-BCE6-AC132C9C6BAF}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
--- a/Config/Config.xlsx
+++ b/Config/Config.xlsx
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="22" uniqueCount="22">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="20" uniqueCount="20">
   <si>
     <t>Name</t>
   </si>
@@ -73,12 +73,6 @@
     <t>Fiscal Year,Period,Week,TML Ref No,Dealer Invoice No,Dealer Invoice Date,IRN No,Ack No,Ack Date,Invoice Type,Plant,Customer Number,Material Amount,Labour Amount,Total Value,CGST,SGST,UGST,IGST,Credit Amount,TDS,Reverse Charges,Accounting Doc No,Remarks</t>
   </si>
   <si>
-    <t>ProfileName</t>
-  </si>
-  <si>
-    <t>TML</t>
-  </si>
-  <si>
     <t>chrome</t>
   </si>
   <si>
@@ -97,10 +91,10 @@
     <t>CleanUpDayCount</t>
   </si>
   <si>
-    <t>Other_Credentials</t>
-  </si>
-  <si>
-    <t>Login_Credentials</t>
+    <t>Assets</t>
+  </si>
+  <si>
+    <t>NextGenCredentials</t>
   </si>
 </sst>
 </file>
@@ -492,7 +486,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:B15"/>
+  <dimension ref="A1:B14"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <cols>
     <col min="1" max="1" width="40.875" customWidth="1"/>
@@ -520,7 +514,7 @@
         <v>2</v>
       </c>
       <c r="B3" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
     </row>
     <row r="4" spans="1:2">
@@ -536,15 +530,15 @@
         <v>6</v>
       </c>
       <c r="B5" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
     </row>
     <row r="6" spans="1:2">
       <c r="A6" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="B6" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
     </row>
     <row r="7" spans="1:2">
@@ -552,7 +546,7 @@
         <v>5</v>
       </c>
       <c r="B7" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
     </row>
     <row r="8" spans="1:2">
@@ -573,33 +567,25 @@
     </row>
     <row r="10" spans="1:2">
       <c r="A10" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="B10" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
     </row>
     <row r="11" spans="1:2">
       <c r="A11" t="s">
         <v>17</v>
       </c>
-      <c r="B11" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="12" spans="1:2">
-      <c r="A12" t="s">
-        <v>19</v>
-      </c>
-      <c r="B12">
+      <c r="B11">
         <v>7</v>
       </c>
+    </row>
+    <row r="13" spans="1:2">
+      <c r="B13" s="2"/>
     </row>
     <row r="14" spans="1:2">
       <c r="B14" s="2"/>
-    </row>
-    <row r="15" spans="1:2">
-      <c r="B15" s="2"/>
     </row>
   </sheetData>
   <hyperlinks>
@@ -611,17 +597,6 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <TaxCatchAll xmlns="399697c3-5931-482a-bf60-528e1410a718" xsi:nil="true"/>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="69774094-9380-4fae-b934-13dda1a7dd00">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-  </documentManagement>
-</p:properties>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x01010044376E494BD8C84F84CDAE7F49671CB7" ma:contentTypeVersion="18" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="976d064ff5353b1784c9cc50294987ed">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="69774094-9380-4fae-b934-13dda1a7dd00" xmlns:ns3="399697c3-5931-482a-bf60-528e1410a718" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="6d25ac32989da96868f130ee3b29a1a8" ns2:_="" ns3:_="">
     <xsd:import namespace="69774094-9380-4fae-b934-13dda1a7dd00"/>
@@ -876,6 +851,17 @@
 </ct:contentTypeSchema>
 </file>
 
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <TaxCatchAll xmlns="399697c3-5931-482a-bf60-528e1410a718" xsi:nil="true"/>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="69774094-9380-4fae-b934-13dda1a7dd00">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+  </documentManagement>
+</p:properties>
+</file>
+
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <?mso-contentType ?>
 <FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
@@ -886,17 +872,6 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E2F655CD-E750-4B4F-AAB6-574220BB7DEF}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="399697c3-5931-482a-bf60-528e1410a718"/>
-    <ds:schemaRef ds:uri="69774094-9380-4fae-b934-13dda1a7dd00"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{14112939-A704-4318-9B1F-3D369493ECFB}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -915,6 +890,17 @@
 </ds:datastoreItem>
 </file>
 
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E2F655CD-E750-4B4F-AAB6-574220BB7DEF}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="399697c3-5931-482a-bf60-528e1410a718"/>
+    <ds:schemaRef ds:uri="69774094-9380-4fae-b934-13dda1a7dd00"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{4B24F227-3507-4068-BCE6-AC132C9C6BAF}">
   <ds:schemaRefs>
